--- a/PT Tourney Data Inventory.xlsx
+++ b/PT Tourney Data Inventory.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Perfect Drafts'!$A$4:$Q$62</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Tournaments!$A$4:$Q$120</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Tournaments!$A$4:$Q$123</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="485">
   <si>
     <t xml:space="preserve">Tournaments — stat-export coverage</t>
   </si>
@@ -136,10 +136,10 @@
     <t xml:space="preserve">diamondslotsdaily</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1800166, 1800167, 1800168, 1800169, 1800170, 1800171</t>
+    <t xml:space="preserve">2026-08-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1800166, 1800168, 1800169, 1800170, 1800171</t>
   </si>
   <si>
     <t xml:space="preserve">Daily Diamonds are Forever</t>
@@ -226,10 +226,10 @@
     <t xml:space="preserve">diamondvariety</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1590023, 1590024</t>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1590023</t>
   </si>
   <si>
     <t xml:space="preserve">Diamond Quick</t>
@@ -277,7 +277,7 @@
     <t xml:space="preserve">goldenheart</t>
   </si>
   <si>
-    <t xml:space="preserve">1840148, 1840149, 1840150, 1840151, 1840152, 1840153, 1840154</t>
+    <t xml:space="preserve">1840148, 1840149, 1840150, 1840152, 1840153, 1840154</t>
   </si>
   <si>
     <t xml:space="preserve">40-89</t>
@@ -304,7 +304,7 @@
     <t xml:space="preserve">goldslotsdaily</t>
   </si>
   <si>
-    <t xml:space="preserve">1320168, 1320169, 1320170</t>
+    <t xml:space="preserve">1320170</t>
   </si>
   <si>
     <t xml:space="preserve">Daily Low Gold Retrospecticus</t>
@@ -316,10 +316,7 @@
     <t xml:space="preserve">lgretro</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1660160, 1660161, 1660162, 1660163, 1660164, 1660165, 1660166</t>
+    <t xml:space="preserve">1660160, 1660161, 1660162, 1660163, 1660166</t>
   </si>
   <si>
     <t xml:space="preserve">40-84</t>
@@ -334,10 +331,7 @@
     <t xml:space="preserve">goldenchildhood</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1910090, 1910091, 1910092, 1910093, 1910094, 1910095, 1910096</t>
+    <t xml:space="preserve">1910090, 1910091, 1910092, 1910094, 1910095, 1910096</t>
   </si>
   <si>
     <t xml:space="preserve">Daily Goldfather II</t>
@@ -379,9 +373,6 @@
     <t xml:space="preserve">highironfloorgoldceilingweekly</t>
   </si>
   <si>
-    <t xml:space="preserve">1600024</t>
-  </si>
-  <si>
     <t xml:space="preserve">50-89</t>
   </si>
   <si>
@@ -394,40 +385,40 @@
     <t xml:space="preserve">goldweekly</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-27</t>
-  </si>
-  <si>
     <t xml:space="preserve">1530024</t>
   </si>
   <si>
+    <t xml:space="preserve">Monday Wonky Historical Slots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1430023, 1430024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily Gold Cap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily Live Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EF 4T Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EF H2H Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gold Quick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low Gold Quick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">low gold</t>
+  </si>
+  <si>
     <t xml:space="preserve">Daily Low Gold Retrospectus</t>
   </si>
   <si>
-    <t xml:space="preserve">Monday Wonky Historical Slots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1430023, 1430024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily Gold Cap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily Live Gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EF 4T Gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EF H2H Gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gold Quick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low Gold Quick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">low gold</t>
+    <t xml:space="preserve">duplicate listing — exports counted on "Daily Low Gold Retrospecticus"</t>
   </si>
   <si>
     <t xml:space="preserve">Silver</t>
@@ -442,7 +433,10 @@
     <t xml:space="preserve">latesilver</t>
   </si>
   <si>
-    <t xml:space="preserve">1240164, 1240168, 1240169, 1240170</t>
+    <t xml:space="preserve">2026-08-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1240164, 1240169, 1240170</t>
   </si>
   <si>
     <t xml:space="preserve">40-79</t>
@@ -457,60 +451,57 @@
     <t xml:space="preserve">silverandfriends</t>
   </si>
   <si>
+    <t xml:space="preserve">1900091, 1900092, 1900093, 1900094, 1900096, 1900097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily Silver Slamboree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silverslamboree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1650161, 1650162, 1650163, 1650166, 1650167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily Silver Heart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silverheart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1830148, 1830149, 1830150, 1830152, 1830153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily Silver Slots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silverslotsdaily</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1270165, 1270166, 1270168, 1270170</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily Live Silver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">livesilverdaily</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026-07-31</t>
   </si>
   <si>
-    <t xml:space="preserve">1900091, 1900092, 1900093, 1900094, 1900095, 1900096, 1900097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily Silver Slamboree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">silverslamboree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1650161, 1650162, 1650163, 1650164, 1650165, 1650166, 1650167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily Silver Heart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">silverheart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1830148, 1830149, 1830150, 1830151, 1830152, 1830153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily Silver Slots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">silverslotsdaily</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1270165, 1270166, 1270168, 1270170</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily Live Silver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">livesilverdaily</t>
-  </si>
-  <si>
     <t xml:space="preserve">1260164, 1260165, 1260166, 1260167, 1260168, 1260169, 1260170</t>
   </si>
   <si>
@@ -646,6 +637,15 @@
     <t xml:space="preserve">Saturday Bronze Cap</t>
   </si>
   <si>
+    <t xml:space="preserve">(series "bronzesequel")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bronzesequel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">series not linked to a catalog tournament</t>
+  </si>
+  <si>
     <t xml:space="preserve">Daily Bronze The Sequel</t>
   </si>
   <si>
@@ -859,31 +859,34 @@
     <t xml:space="preserve">MISMATCH — file numbers are on a different counter</t>
   </si>
   <si>
+    <t xml:space="preserve">Daily Open High Cap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1390164, 1390165, 1390166, 1390167, 1390168, 1390169, 1390170</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily Open Low Cap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thursday Mishmash Cap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thursday CWhit's Cap Challenge 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">retired — slot 187 is now "Thursday CWhit's Cap Challenge 4"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thursday CWhit's Cap Challenge 2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Thursday CWhit's Cap Challenge</t>
   </si>
   <si>
-    <t xml:space="preserve">Daily Open High Cap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1390164, 1390165, 1390166, 1390167, 1390168, 1390169, 1390170</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily Open Low Cap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thursday Mishmash Cap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thursday CWhit's Cap Challenge 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">retired — slot 187 is now "Thursday CWhit's Cap Challenge 4"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thursday CWhit's Cap Challenge 2</t>
+    <t xml:space="preserve">duplicate listing — exports counted on "Thursday CWhit's Cap Challenge 4"</t>
   </si>
   <si>
     <t xml:space="preserve">Other</t>
@@ -907,49 +910,64 @@
     <t xml:space="preserve">1950tonow</t>
   </si>
   <si>
+    <t xml:space="preserve">Dr. Dynastic's Daily Time Travelers Slots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cwhit 4.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cwhit4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily Negro Leagues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily Time Travelers Slots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Custom Tournament</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTMS 2 Tourney 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTMS 2 Tourney 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTMS 2 Tourney 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quick Dank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saturday Negro Leagues Slots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(series "strugglingsleep")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">strugglingsleep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(series "wonkyslots")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wonkyslots</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tuesday Up To 1969</t>
   </si>
   <si>
-    <t xml:space="preserve">Dr. Dynastic's Daily Time Travelers Slots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cwhit 4.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cwhit4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily Negro Leagues</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily Time Travelers Slots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My Custom Tournament</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PTMS 2 Tourney 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PTMS 2 Tourney 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PTMS 2 Tourney 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quick Dank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saturday Negro Leagues Slots</t>
+    <t xml:space="preserve">duplicate listing — exports counted on "Tuesday Up to 1969"</t>
   </si>
   <si>
     <t xml:space="preserve">Perfect Drafts — stat-export coverage</t>
   </si>
   <si>
-    <t xml:space="preserve">Same columns. Only two draft series have ever been exported, and PD Daily is your biggest points category. Generated 2026-08-31.</t>
+    <t xml:space="preserve">Same columns. PD Daily is the biggest points category and the thinnest data. Generated 2026-08-31.</t>
   </si>
   <si>
     <t xml:space="preserve">Laptophound's Daily 5L Deadball</t>
@@ -1450,7 +1468,7 @@
     <t xml:space="preserve">• PT id — the first three digits of an event id. A run is &lt;PT id&gt;&lt;4-digit run&gt;, so tournament 185 run 151 is event 1850151.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Still running? — OOTP REUSES an id slot when a tournament is renamed. Slot 218 was Treasure Trove until Aug 6 and is 6L Power Play now. A row that names a successor is retired: its runs cannot be exported and those ids belong to the new event.</t>
+    <t xml:space="preserve">• Still running? — OOTP REUSES an id slot when a tournament is renamed. Slot 218 was Treasure Trove until Aug 6 and is 6L Power Play now. A row naming a successor is retired: its runs cannot be exported and those ids belong to the new event.</t>
   </si>
   <si>
     <t xml:space="preserve">• Runs on file vs Files — "Runs on file" is what the database imported, "Files" is what sits in Archive/Completed. A gap means pnpm import:observed has not been run.</t>
@@ -2213,7 +2231,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q120"/>
+  <dimension ref="A1:Q123"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -2416,22 +2434,22 @@
         <v>35</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>36</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>37</v>
@@ -2732,22 +2750,22 @@
         <v>65</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>2</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>66</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K13" s="5" t="s">
         <v>67</v>
@@ -3025,22 +3043,22 @@
         <v>82</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>15</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K20" s="5" t="s">
         <v>83</v>
@@ -3131,22 +3149,22 @@
         <v>91</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K22" s="5" t="s">
         <v>92</v>
@@ -3184,28 +3202,28 @@
         <v>95</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="F23" s="8" t="n">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>13</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="H23" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K23" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="I23" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="K23" s="5" t="s">
+      <c r="L23" s="5" t="s">
         <v>97</v>
-      </c>
-      <c r="L23" s="5" t="s">
-        <v>98</v>
       </c>
       <c r="M23" s="6" t="n">
         <v>64</v>
@@ -3228,34 +3246,34 @@
         <v>79</v>
       </c>
       <c r="B24" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="D24" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="E24" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="K24" s="5" t="s">
         <v>101</v>
-      </c>
-      <c r="E24" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>72</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>103</v>
       </c>
       <c r="L24" s="5" t="s">
         <v>84</v>
@@ -3281,13 +3299,13 @@
         <v>79</v>
       </c>
       <c r="B25" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>106</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>8</v>
@@ -3299,7 +3317,7 @@
         <v>130</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>40</v>
@@ -3308,7 +3326,7 @@
         <v>7</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="L25" s="5" t="s">
         <v>84</v>
@@ -3334,13 +3352,13 @@
         <v>79</v>
       </c>
       <c r="B26" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="D26" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>111</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>1</v>
@@ -3361,10 +3379,10 @@
         <v>1</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="L26" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M26" s="6" t="n">
         <v>128</v>
@@ -3387,37 +3405,35 @@
         <v>79</v>
       </c>
       <c r="B27" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D27" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="E27" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5" t="s">
         <v>115</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="E27" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F27" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G27" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="J27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="L27" s="5" t="s">
-        <v>118</v>
       </c>
       <c r="M27" s="6" t="n">
         <v>128</v>
@@ -3440,13 +3456,13 @@
         <v>79</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E28" s="6" t="n">
         <v>1</v>
@@ -3458,7 +3474,7 @@
         <v>23</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>122</v>
+        <v>36</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>4</v>
@@ -3467,7 +3483,7 @@
         <v>1</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="L28" s="5" t="s">
         <v>84</v>
@@ -3493,38 +3509,38 @@
         <v>79</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5" t="s">
-        <v>95</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D29" s="5"/>
       <c r="E29" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="F29" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="G29" s="6" t="n">
-        <v>147</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="5"/>
       <c r="H29" s="5"/>
       <c r="I29" s="5"/>
       <c r="J29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="5"/>
+        <v>2</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>121</v>
+      </c>
       <c r="L29" s="5" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P29" s="5" t="s">
         <v>26</v>
@@ -3538,11 +3554,9 @@
         <v>79</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>77</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="E30" s="6" t="n">
         <v>0</v>
@@ -3554,22 +3568,20 @@
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K30" s="5" t="s">
-        <v>126</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K30" s="5"/>
       <c r="L30" s="5" t="s">
         <v>84</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P30" s="5" t="s">
         <v>26</v>
@@ -3583,7 +3595,7 @@
         <v>79</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
@@ -3604,7 +3616,7 @@
         <v>84</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="N31" s="6" t="n">
         <v>0</v>
@@ -3624,7 +3636,7 @@
         <v>79</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -3645,7 +3657,7 @@
         <v>84</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>128</v>
+        <v>4</v>
       </c>
       <c r="N32" s="6" t="n">
         <v>0</v>
@@ -3665,7 +3677,7 @@
         <v>79</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
@@ -3686,7 +3698,7 @@
         <v>84</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N33" s="6" t="n">
         <v>0</v>
@@ -3706,7 +3718,7 @@
         <v>79</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
@@ -3727,7 +3739,7 @@
         <v>84</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="N34" s="6" t="n">
         <v>0</v>
@@ -3747,7 +3759,7 @@
         <v>79</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
@@ -3764,12 +3776,8 @@
         <v>0</v>
       </c>
       <c r="K35" s="5"/>
-      <c r="L35" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="M35" s="6" t="n">
-        <v>16</v>
-      </c>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
       <c r="N35" s="6" t="n">
         <v>0</v>
       </c>
@@ -3788,7 +3796,7 @@
         <v>79</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
@@ -3825,10 +3833,12 @@
         <v>79</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
+      <c r="D37" s="5" t="s">
+        <v>95</v>
+      </c>
       <c r="E37" s="6" t="n">
         <v>0</v>
       </c>
@@ -3842,16 +3852,20 @@
         <v>0</v>
       </c>
       <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
-      <c r="M37" s="5"/>
+      <c r="L37" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="M37" s="6" t="n">
+        <v>64</v>
+      </c>
       <c r="N37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="O37" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="P37" s="5" t="s">
-        <v>26</v>
+      <c r="P37" s="10" t="s">
+        <v>130</v>
       </c>
       <c r="Q37" s="5" t="s">
         <v>70</v>
@@ -3859,40 +3873,40 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D38" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="E38" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>168</v>
+      </c>
+      <c r="H38" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="I38" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J38" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K38" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="L38" s="5" t="s">
         <v>137</v>
-      </c>
-      <c r="E38" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="F38" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="G38" s="6" t="n">
-        <v>167</v>
-      </c>
-      <c r="H38" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I38" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J38" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="K38" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="L38" s="5" t="s">
-        <v>139</v>
       </c>
       <c r="M38" s="6" t="n">
         <v>64</v>
@@ -3912,37 +3926,37 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B39" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D39" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="E39" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="I39" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J39" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="K39" s="5" t="s">
         <v>141</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="E39" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F39" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G39" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="H39" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="I39" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="J39" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="K39" s="5" t="s">
-        <v>144</v>
       </c>
       <c r="L39" s="5"/>
       <c r="M39" s="6" t="n">
@@ -3963,40 +3977,40 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B40" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="I40" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J40" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K40" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="C40" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="E40" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="F40" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="G40" s="6" t="n">
-        <v>136</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="I40" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="J40" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="K40" s="5" t="s">
-        <v>148</v>
-      </c>
       <c r="L40" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M40" s="6" t="n">
         <v>64</v>
@@ -4016,40 +4030,40 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B41" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F41" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>151</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J41" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K41" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="C41" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="E41" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="F41" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G41" s="6" t="n">
-        <v>147</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I41" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="J41" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="K41" s="5" t="s">
-        <v>152</v>
-      </c>
       <c r="L41" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M41" s="6" t="n">
         <v>64</v>
@@ -4069,19 +4083,19 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F42" s="7" t="n">
         <v>5</v>
@@ -4090,7 +4104,7 @@
         <v>169</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>156</v>
+        <v>66</v>
       </c>
       <c r="I42" s="6" t="n">
         <v>1</v>
@@ -4099,10 +4113,10 @@
         <v>4</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="L42" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M42" s="6" t="n">
         <v>64</v>
@@ -4122,16 +4136,16 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E43" s="6" t="n">
         <v>1</v>
@@ -4143,7 +4157,7 @@
         <v>139</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="I43" s="6" t="n">
         <v>31</v>
@@ -4152,10 +4166,10 @@
         <v>7</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="L43" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M43" s="6" t="n">
         <v>64</v>
@@ -4175,16 +4189,16 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E44" s="6" t="n">
         <v>1</v>
@@ -4196,7 +4210,7 @@
         <v>23</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>122</v>
+        <v>36</v>
       </c>
       <c r="I44" s="6" t="n">
         <v>4</v>
@@ -4205,10 +4219,10 @@
         <v>1</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="L44" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M44" s="6" t="n">
         <v>256</v>
@@ -4228,13 +4242,13 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="6" t="n">
@@ -4250,10 +4264,10 @@
         <v>1</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="L45" s="5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="M45" s="6" t="n">
         <v>128</v>
@@ -4273,10 +4287,10 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
@@ -4294,7 +4308,7 @@
       </c>
       <c r="K46" s="5"/>
       <c r="L46" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M46" s="6" t="n">
         <v>64</v>
@@ -4314,10 +4328,10 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C47" s="5"/>
       <c r="D47" s="5"/>
@@ -4335,7 +4349,7 @@
       </c>
       <c r="K47" s="5"/>
       <c r="L47" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M47" s="6" t="n">
         <v>32</v>
@@ -4355,10 +4369,10 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
@@ -4392,10 +4406,10 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
@@ -4429,10 +4443,10 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
@@ -4450,7 +4464,7 @@
       </c>
       <c r="K50" s="5"/>
       <c r="L50" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M50" s="6" t="n">
         <v>16</v>
@@ -4470,16 +4484,16 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D51" s="5" t="s">
         <v>175</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>178</v>
       </c>
       <c r="E51" s="6" t="n">
         <v>3</v>
@@ -4497,7 +4511,7 @@
       </c>
       <c r="K51" s="5"/>
       <c r="L51" s="5" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="M51" s="6" t="n">
         <v>64</v>
@@ -4517,16 +4531,16 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="13" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E52" s="6" t="n">
         <v>1</v>
@@ -4544,7 +4558,7 @@
       </c>
       <c r="K52" s="5"/>
       <c r="L52" s="5" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="M52" s="6" t="n">
         <v>64</v>
@@ -4564,16 +4578,16 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="13" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E53" s="6" t="n">
         <v>1</v>
@@ -4591,7 +4605,7 @@
       </c>
       <c r="K53" s="5"/>
       <c r="L53" s="5" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="M53" s="6" t="n">
         <v>256</v>
@@ -4611,23 +4625,23 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="13" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C54" s="5"/>
       <c r="D54" s="5" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
@@ -4636,7 +4650,7 @@
       </c>
       <c r="K54" s="5"/>
       <c r="L54" s="5" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="M54" s="6" t="n">
         <v>128</v>
@@ -4656,14 +4670,14 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="13" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C55" s="5"/>
       <c r="D55" s="5" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E55" s="6" t="n">
         <v>2</v>
@@ -4697,13 +4711,13 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="13" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="6" t="n">
@@ -4719,7 +4733,7 @@
         <v>7</v>
       </c>
       <c r="K56" s="5" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="L56" s="5"/>
       <c r="M56" s="6" t="n">
@@ -4740,13 +4754,13 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="13" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="6" t="n">
@@ -4762,7 +4776,7 @@
         <v>7</v>
       </c>
       <c r="K57" s="5" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="L57" s="5"/>
       <c r="M57" s="6" t="n">
@@ -4783,10 +4797,10 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="13" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
@@ -4804,7 +4818,7 @@
       </c>
       <c r="K58" s="5"/>
       <c r="L58" s="5" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="M58" s="6" t="n">
         <v>16</v>
@@ -4824,10 +4838,10 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="13" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
@@ -4863,10 +4877,10 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="13" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
@@ -4902,10 +4916,10 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="13" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C61" s="5"/>
       <c r="D61" s="5"/>
@@ -4923,7 +4937,7 @@
       </c>
       <c r="K61" s="5"/>
       <c r="L61" s="5" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="M61" s="6" t="n">
         <v>64</v>
@@ -4943,10 +4957,10 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="13" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C62" s="5"/>
       <c r="D62" s="5"/>
@@ -4964,7 +4978,7 @@
       </c>
       <c r="K62" s="5"/>
       <c r="L62" s="5" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="M62" s="6" t="n">
         <v>64</v>
@@ -4984,10 +4998,10 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="13" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C63" s="5"/>
       <c r="D63" s="5"/>
@@ -5005,7 +5019,7 @@
       </c>
       <c r="K63" s="5"/>
       <c r="L63" s="5" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="M63" s="6" t="n">
         <v>64</v>
@@ -5025,10 +5039,10 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="13" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C64" s="5"/>
       <c r="D64" s="5"/>
@@ -5062,10 +5076,10 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="13" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C65" s="5"/>
       <c r="D65" s="5"/>
@@ -5083,7 +5097,7 @@
       </c>
       <c r="K65" s="5"/>
       <c r="L65" s="5" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="M65" s="6" t="n">
         <v>2</v>
@@ -5103,10 +5117,10 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="13" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C66" s="5"/>
       <c r="D66" s="5"/>
@@ -5124,7 +5138,7 @@
       </c>
       <c r="K66" s="5"/>
       <c r="L66" s="5" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="M66" s="6" t="n">
         <v>128</v>
@@ -5144,22 +5158,24 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="13" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="D67" s="5"/>
+        <v>203</v>
+      </c>
+      <c r="C67" s="5"/>
+      <c r="D67" s="5" t="s">
+        <v>204</v>
+      </c>
       <c r="E67" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" s="5"/>
+        <v>1</v>
+      </c>
+      <c r="F67" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="6" t="n">
+        <v>156</v>
+      </c>
       <c r="H67" s="5"/>
       <c r="I67" s="5"/>
       <c r="J67" s="6" t="n">
@@ -5167,30 +5183,30 @@
       </c>
       <c r="K67" s="5"/>
       <c r="L67" s="5"/>
-      <c r="M67" s="6" t="n">
-        <v>128</v>
-      </c>
+      <c r="M67" s="5"/>
       <c r="N67" s="6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O67" s="6" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="Q67" s="5" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="14" t="s">
-        <v>208</v>
+      <c r="A68" s="13" t="s">
+        <v>172</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="C68" s="5"/>
+        <v>206</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>174</v>
+      </c>
       <c r="D68" s="5"/>
       <c r="E68" s="6" t="n">
         <v>0</v>
@@ -5205,20 +5221,18 @@
         <v>0</v>
       </c>
       <c r="K68" s="5"/>
-      <c r="L68" s="5" t="s">
-        <v>210</v>
-      </c>
+      <c r="L68" s="5"/>
       <c r="M68" s="6" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="N68" s="6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O68" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" s="5" t="s">
-        <v>26</v>
+        <v>48</v>
+      </c>
+      <c r="P68" s="10" t="s">
+        <v>207</v>
       </c>
       <c r="Q68" s="5" t="s">
         <v>70</v>
@@ -5229,7 +5243,7 @@
         <v>208</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C69" s="5"/>
       <c r="D69" s="5"/>
@@ -5246,8 +5260,12 @@
         <v>0</v>
       </c>
       <c r="K69" s="5"/>
-      <c r="L69" s="5"/>
-      <c r="M69" s="5"/>
+      <c r="L69" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="M69" s="6" t="n">
+        <v>64</v>
+      </c>
       <c r="N69" s="6" t="n">
         <v>0</v>
       </c>
@@ -5266,7 +5284,7 @@
         <v>208</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C70" s="5"/>
       <c r="D70" s="5"/>
@@ -5283,12 +5301,8 @@
         <v>0</v>
       </c>
       <c r="K70" s="5"/>
-      <c r="L70" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="M70" s="6" t="n">
-        <v>32</v>
-      </c>
+      <c r="L70" s="5"/>
+      <c r="M70" s="5"/>
       <c r="N70" s="6" t="n">
         <v>0</v>
       </c>
@@ -5307,7 +5321,7 @@
         <v>208</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C71" s="5"/>
       <c r="D71" s="5"/>
@@ -5324,8 +5338,12 @@
         <v>0</v>
       </c>
       <c r="K71" s="5"/>
-      <c r="L71" s="5"/>
-      <c r="M71" s="5"/>
+      <c r="L71" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="M71" s="6" t="n">
+        <v>32</v>
+      </c>
       <c r="N71" s="6" t="n">
         <v>0</v>
       </c>
@@ -5344,7 +5362,7 @@
         <v>208</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C72" s="5"/>
       <c r="D72" s="5"/>
@@ -5381,7 +5399,7 @@
         <v>208</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
@@ -5398,12 +5416,8 @@
         <v>0</v>
       </c>
       <c r="K73" s="5"/>
-      <c r="L73" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="M73" s="6" t="n">
-        <v>64</v>
-      </c>
+      <c r="L73" s="5"/>
+      <c r="M73" s="5"/>
       <c r="N73" s="6" t="n">
         <v>0</v>
       </c>
@@ -5422,7 +5436,7 @@
         <v>208</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C74" s="5"/>
       <c r="D74" s="5"/>
@@ -5463,7 +5477,7 @@
         <v>208</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C75" s="5"/>
       <c r="D75" s="5"/>
@@ -5480,8 +5494,12 @@
         <v>0</v>
       </c>
       <c r="K75" s="5"/>
-      <c r="L75" s="5"/>
-      <c r="M75" s="5"/>
+      <c r="L75" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="M75" s="6" t="n">
+        <v>64</v>
+      </c>
       <c r="N75" s="6" t="n">
         <v>0</v>
       </c>
@@ -5500,7 +5518,7 @@
         <v>208</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C76" s="5"/>
       <c r="D76" s="5"/>
@@ -5537,7 +5555,7 @@
         <v>208</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>
@@ -5574,7 +5592,7 @@
         <v>208</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C78" s="5"/>
       <c r="D78" s="5"/>
@@ -5591,12 +5609,8 @@
         <v>0</v>
       </c>
       <c r="K78" s="5"/>
-      <c r="L78" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="M78" s="6" t="n">
-        <v>256</v>
-      </c>
+      <c r="L78" s="5"/>
+      <c r="M78" s="5"/>
       <c r="N78" s="6" t="n">
         <v>0</v>
       </c>
@@ -5615,7 +5629,7 @@
         <v>208</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C79" s="5"/>
       <c r="D79" s="5"/>
@@ -5633,10 +5647,10 @@
       </c>
       <c r="K79" s="5"/>
       <c r="L79" s="5" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="M79" s="6" t="n">
-        <v>16</v>
+        <v>256</v>
       </c>
       <c r="N79" s="6" t="n">
         <v>0</v>
@@ -5656,7 +5670,7 @@
         <v>208</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C80" s="5"/>
       <c r="D80" s="5"/>
@@ -5673,8 +5687,12 @@
         <v>0</v>
       </c>
       <c r="K80" s="5"/>
-      <c r="L80" s="5"/>
-      <c r="M80" s="5"/>
+      <c r="L80" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="M80" s="6" t="n">
+        <v>16</v>
+      </c>
       <c r="N80" s="6" t="n">
         <v>0</v>
       </c>
@@ -5693,7 +5711,7 @@
         <v>208</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C81" s="5"/>
       <c r="D81" s="5"/>
@@ -5710,12 +5728,8 @@
         <v>0</v>
       </c>
       <c r="K81" s="5"/>
-      <c r="L81" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="M81" s="6" t="n">
-        <v>64</v>
-      </c>
+      <c r="L81" s="5"/>
+      <c r="M81" s="5"/>
       <c r="N81" s="6" t="n">
         <v>0</v>
       </c>
@@ -5734,7 +5748,7 @@
         <v>208</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C82" s="5"/>
       <c r="D82" s="5"/>
@@ -5755,72 +5769,60 @@
         <v>213</v>
       </c>
       <c r="M82" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="N82" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q82" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C83" s="5"/>
+      <c r="D83" s="5"/>
+      <c r="E83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="5"/>
+      <c r="H83" s="5"/>
+      <c r="I83" s="5"/>
+      <c r="J83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="5"/>
+      <c r="L83" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="M83" s="6" t="n">
         <v>256</v>
       </c>
-      <c r="N82" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q82" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="C83" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="D83" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="E83" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F83" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="6" t="n">
-        <v>88</v>
-      </c>
-      <c r="H83" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="I83" s="6" t="n">
-        <v>82</v>
-      </c>
-      <c r="J83" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="K83" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="L83" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="M83" s="6" t="n">
-        <v>128</v>
-      </c>
       <c r="N83" s="6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O83" s="6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P83" s="5" t="s">
         <v>26</v>
       </c>
       <c r="Q83" s="5" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5828,13 +5830,13 @@
         <v>226</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="E84" s="6" t="n">
         <v>1</v>
@@ -5843,31 +5845,31 @@
         <v>1</v>
       </c>
       <c r="G84" s="6" t="n">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="I84" s="6" t="n">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="J84" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K84" s="5" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L84" s="5" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M84" s="6" t="n">
         <v>128</v>
       </c>
       <c r="N84" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O84" s="6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="P84" s="5" t="s">
         <v>26</v>
@@ -5881,44 +5883,46 @@
         <v>226</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="E85" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="H85" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="I85" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="J85" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F85" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G85" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="H85" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I85" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="J85" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="K85" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="L85" s="5"/>
+        <v>237</v>
+      </c>
+      <c r="L85" s="5" t="s">
+        <v>238</v>
+      </c>
       <c r="M85" s="6" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="N85" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O85" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P85" s="5" t="s">
         <v>26</v>
@@ -5932,13 +5936,13 @@
         <v>226</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E86" s="6" t="n">
         <v>2</v>
@@ -5947,29 +5951,29 @@
         <v>2</v>
       </c>
       <c r="G86" s="6" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>246</v>
+        <v>41</v>
       </c>
       <c r="I86" s="6" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="J86" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K86" s="5" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="L86" s="5"/>
       <c r="M86" s="6" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="N86" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O86" s="6" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P86" s="5" t="s">
         <v>26</v>
@@ -5983,44 +5987,44 @@
         <v>226</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E87" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F87" s="7" t="n">
+      <c r="F87" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G87" s="6" t="n">
-        <v>167</v>
+        <v>19</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>23</v>
+        <v>246</v>
       </c>
       <c r="I87" s="6" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="J87" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K87" s="5" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="L87" s="5"/>
       <c r="M87" s="6" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="N87" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O87" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P87" s="5" t="s">
         <v>26</v>
@@ -6034,44 +6038,44 @@
         <v>226</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G88" s="6" t="n">
+        <v>167</v>
+      </c>
+      <c r="H88" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H88" s="5" t="s">
-        <v>122</v>
-      </c>
       <c r="I88" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J88" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K88" s="5" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="L88" s="5"/>
       <c r="M88" s="6" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="N88" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O88" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P88" s="5" t="s">
         <v>26</v>
@@ -6085,44 +6089,50 @@
         <v>226</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="D89" s="5"/>
+        <v>253</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>254</v>
+      </c>
       <c r="E89" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" s="5"/>
-      <c r="H89" s="5"/>
-      <c r="I89" s="5"/>
+        <v>1</v>
+      </c>
+      <c r="F89" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="H89" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I89" s="6" t="n">
+        <v>4</v>
+      </c>
       <c r="J89" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K89" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="L89" s="5" t="s">
-        <v>232</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="L89" s="5"/>
       <c r="M89" s="6" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="N89" s="6" t="n">
         <v>2</v>
       </c>
       <c r="O89" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P89" s="5" t="s">
         <v>26</v>
       </c>
       <c r="Q89" s="5" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6130,10 +6140,10 @@
         <v>226</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D90" s="5"/>
       <c r="E90" s="6" t="n">
@@ -6146,20 +6156,22 @@
       <c r="H90" s="5"/>
       <c r="I90" s="5"/>
       <c r="J90" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" s="5"/>
+        <v>2</v>
+      </c>
+      <c r="K90" s="5" t="s">
+        <v>258</v>
+      </c>
       <c r="L90" s="5" t="s">
-        <v>261</v>
+        <v>232</v>
       </c>
       <c r="M90" s="6" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="N90" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="O90" s="6" t="n">
         <v>1</v>
-      </c>
-      <c r="O90" s="6" t="n">
-        <v>0</v>
       </c>
       <c r="P90" s="5" t="s">
         <v>26</v>
@@ -6173,9 +6185,11 @@
         <v>226</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="C91" s="5"/>
+        <v>259</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>260</v>
+      </c>
       <c r="D91" s="5"/>
       <c r="E91" s="6" t="n">
         <v>0</v>
@@ -6194,10 +6208,10 @@
         <v>261</v>
       </c>
       <c r="M91" s="6" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="N91" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O91" s="6" t="n">
         <v>0</v>
@@ -6214,7 +6228,7 @@
         <v>226</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C92" s="5"/>
       <c r="D92" s="5"/>
@@ -6235,7 +6249,7 @@
         <v>261</v>
       </c>
       <c r="M92" s="6" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="N92" s="6" t="n">
         <v>0</v>
@@ -6255,7 +6269,7 @@
         <v>226</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C93" s="5"/>
       <c r="D93" s="5"/>
@@ -6276,7 +6290,7 @@
         <v>261</v>
       </c>
       <c r="M93" s="6" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="N93" s="6" t="n">
         <v>0</v>
@@ -6296,7 +6310,7 @@
         <v>226</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C94" s="5"/>
       <c r="D94" s="5"/>
@@ -6313,8 +6327,12 @@
         <v>0</v>
       </c>
       <c r="K94" s="5"/>
-      <c r="L94" s="5"/>
-      <c r="M94" s="5"/>
+      <c r="L94" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="M94" s="6" t="n">
+        <v>64</v>
+      </c>
       <c r="N94" s="6" t="n">
         <v>0</v>
       </c>
@@ -6333,7 +6351,7 @@
         <v>226</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C95" s="5"/>
       <c r="D95" s="5"/>
@@ -6370,7 +6388,7 @@
         <v>226</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C96" s="5"/>
       <c r="D96" s="5"/>
@@ -6387,12 +6405,8 @@
         <v>0</v>
       </c>
       <c r="K96" s="5"/>
-      <c r="L96" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="M96" s="6" t="n">
-        <v>16</v>
-      </c>
+      <c r="L96" s="5"/>
+      <c r="M96" s="5"/>
       <c r="N96" s="6" t="n">
         <v>0</v>
       </c>
@@ -6411,7 +6425,7 @@
         <v>226</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C97" s="5"/>
       <c r="D97" s="5"/>
@@ -6428,8 +6442,12 @@
         <v>0</v>
       </c>
       <c r="K97" s="5"/>
-      <c r="L97" s="5"/>
-      <c r="M97" s="5"/>
+      <c r="L97" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="M97" s="6" t="n">
+        <v>16</v>
+      </c>
       <c r="N97" s="6" t="n">
         <v>0</v>
       </c>
@@ -6448,7 +6466,7 @@
         <v>226</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C98" s="5"/>
       <c r="D98" s="5"/>
@@ -6481,11 +6499,11 @@
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="16" t="s">
-        <v>270</v>
+      <c r="A99" s="15" t="s">
+        <v>226</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C99" s="5"/>
       <c r="D99" s="5"/>
@@ -6518,52 +6536,40 @@
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="17" t="s">
-        <v>272</v>
+      <c r="A100" s="16" t="s">
+        <v>270</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="D100" s="5" t="s">
-        <v>275</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="C100" s="5"/>
+      <c r="D100" s="5"/>
       <c r="E100" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F100" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G100" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="H100" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="I100" s="6" t="n">
-        <v>4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F100" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="5"/>
+      <c r="H100" s="5"/>
+      <c r="I100" s="5"/>
       <c r="J100" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K100" s="5"/>
       <c r="L100" s="5"/>
-      <c r="M100" s="6" t="n">
-        <v>128</v>
-      </c>
+      <c r="M100" s="5"/>
       <c r="N100" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O100" s="6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P100" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="Q100" s="18" t="s">
-        <v>276</v>
+      <c r="Q100" s="5" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6571,9 +6577,11 @@
         <v>272</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="C101" s="5"/>
+        <v>273</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>274</v>
+      </c>
       <c r="D101" s="5" t="s">
         <v>275</v>
       </c>
@@ -6586,8 +6594,12 @@
       <c r="G101" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="H101" s="5"/>
-      <c r="I101" s="5"/>
+      <c r="H101" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I101" s="6" t="n">
+        <v>4</v>
+      </c>
       <c r="J101" s="6" t="n">
         <v>0</v>
       </c>
@@ -6597,16 +6609,16 @@
         <v>128</v>
       </c>
       <c r="N101" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O101" s="6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P101" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="Q101" s="5" t="s">
-        <v>70</v>
+      <c r="Q101" s="18" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6614,10 +6626,10 @@
         <v>272</v>
       </c>
       <c r="B102" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="C102" s="5" t="s">
         <v>278</v>
-      </c>
-      <c r="C102" s="5" t="s">
-        <v>279</v>
       </c>
       <c r="D102" s="5"/>
       <c r="E102" s="6" t="n">
@@ -6633,7 +6645,7 @@
         <v>7</v>
       </c>
       <c r="K102" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L102" s="5"/>
       <c r="M102" s="6" t="n">
@@ -6657,7 +6669,7 @@
         <v>272</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C103" s="5"/>
       <c r="D103" s="5"/>
@@ -6696,7 +6708,7 @@
         <v>272</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C104" s="5"/>
       <c r="D104" s="5"/>
@@ -6733,7 +6745,7 @@
         <v>272</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C105" s="5" t="s">
         <v>274</v>
@@ -6742,20 +6754,14 @@
         <v>275</v>
       </c>
       <c r="E105" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F105" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G105" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="H105" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="I105" s="6" t="n">
-        <v>4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F105" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="5"/>
+      <c r="H105" s="5"/>
+      <c r="I105" s="5"/>
       <c r="J105" s="6" t="n">
         <v>0</v>
       </c>
@@ -6771,7 +6777,7 @@
         <v>2</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q105" s="18" t="s">
         <v>276</v>
@@ -6782,7 +6788,7 @@
         <v>272</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C106" s="5" t="s">
         <v>274</v>
@@ -6791,20 +6797,14 @@
         <v>275</v>
       </c>
       <c r="E106" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F106" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G106" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="H106" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="I106" s="6" t="n">
-        <v>4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="5"/>
+      <c r="H106" s="5"/>
+      <c r="I106" s="5"/>
       <c r="J106" s="6" t="n">
         <v>0</v>
       </c>
@@ -6820,34 +6820,30 @@
         <v>4</v>
       </c>
       <c r="P106" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q106" s="18" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="19" t="s">
-        <v>286</v>
+      <c r="A107" s="17" t="s">
+        <v>272</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>288</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="C107" s="5"/>
       <c r="D107" s="5" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="E107" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F107" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G107" s="6" t="n">
-        <v>23</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="5"/>
       <c r="H107" s="5"/>
       <c r="I107" s="5"/>
       <c r="J107" s="6" t="n">
@@ -6859,13 +6855,13 @@
         <v>128</v>
       </c>
       <c r="N107" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O107" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="P107" s="5" t="s">
-        <v>26</v>
+      <c r="P107" s="10" t="s">
+        <v>286</v>
       </c>
       <c r="Q107" s="5" t="s">
         <v>70</v>
@@ -6873,22 +6869,22 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B108" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="D108" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="C108" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="D108" s="5" t="s">
-        <v>292</v>
-      </c>
       <c r="E108" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F108" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G108" s="6" t="n">
         <v>23</v>
@@ -6918,20 +6914,22 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B109" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="D109" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="C109" s="5"/>
-      <c r="D109" s="5" t="s">
-        <v>289</v>
-      </c>
       <c r="E109" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F109" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G109" s="6" t="n">
         <v>23</v>
@@ -6947,7 +6945,7 @@
         <v>128</v>
       </c>
       <c r="N109" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O109" s="6" t="n">
         <v>0</v>
@@ -6961,7 +6959,7 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>294</v>
@@ -7002,7 +7000,7 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>296</v>
@@ -7039,7 +7037,7 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>297</v>
@@ -7076,7 +7074,7 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>298</v>
@@ -7115,7 +7113,7 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>299</v>
@@ -7154,7 +7152,7 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>300</v>
@@ -7191,7 +7189,7 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>301</v>
@@ -7228,7 +7226,7 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>302</v>
@@ -7265,7 +7263,7 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>303</v>
@@ -7302,7 +7300,7 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>304</v>
@@ -7341,7 +7339,7 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>305</v>
@@ -7378,8 +7376,131 @@
         <v>70</v>
       </c>
     </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="C121" s="5"/>
+      <c r="D121" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E121" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" s="6" t="n">
+        <v>169</v>
+      </c>
+      <c r="H121" s="5"/>
+      <c r="I121" s="5"/>
+      <c r="J121" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" s="5"/>
+      <c r="L121" s="5"/>
+      <c r="M121" s="5"/>
+      <c r="N121" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q121" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="C122" s="5"/>
+      <c r="D122" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="E122" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="H122" s="5"/>
+      <c r="I122" s="5"/>
+      <c r="J122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" s="5"/>
+      <c r="L122" s="5"/>
+      <c r="M122" s="5"/>
+      <c r="N122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q122" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="C123" s="5"/>
+      <c r="D123" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="E123" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" s="5"/>
+      <c r="H123" s="5"/>
+      <c r="I123" s="5"/>
+      <c r="J123" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" s="5"/>
+      <c r="L123" s="5"/>
+      <c r="M123" s="6" t="n">
+        <v>128</v>
+      </c>
+      <c r="N123" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q123" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:Q120"/>
+  <autoFilter ref="A4:Q123"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -7420,12 +7541,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7483,16 +7604,16 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>6</v>
@@ -7513,10 +7634,10 @@
         <v>3</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M5" s="6" t="n">
         <v>128</v>
@@ -7539,13 +7660,13 @@
         <v>79</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>7</v>
@@ -7566,7 +7687,7 @@
         <v>3</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="L6" s="5" t="s">
         <v>84</v>
@@ -7589,13 +7710,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="6" t="n">
@@ -7611,7 +7732,7 @@
         <v>7</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="L7" s="5"/>
       <c r="M7" s="6" t="n">
@@ -7632,13 +7753,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="6" t="n">
@@ -7654,7 +7775,7 @@
         <v>7</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="6" t="n">
@@ -7678,10 +7799,10 @@
         <v>270</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="6" t="n">
@@ -7697,7 +7818,7 @@
         <v>7</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="L9" s="5"/>
       <c r="M9" s="6" t="n">
@@ -7721,10 +7842,10 @@
         <v>270</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="6" t="n">
@@ -7740,7 +7861,7 @@
         <v>7</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="L10" s="5"/>
       <c r="M10" s="6" t="n">
@@ -7764,10 +7885,10 @@
         <v>270</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="6" t="n">
@@ -7783,7 +7904,7 @@
         <v>7</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="L11" s="5"/>
       <c r="M11" s="6" t="n">
@@ -7804,13 +7925,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="6" t="n">
@@ -7826,7 +7947,7 @@
         <v>7</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="L12" s="5"/>
       <c r="M12" s="6" t="n">
@@ -7847,13 +7968,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="6" t="n">
@@ -7869,7 +7990,7 @@
         <v>7</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="L13" s="5"/>
       <c r="M13" s="6" t="n">
@@ -7890,13 +8011,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="6" t="n">
@@ -7912,7 +8033,7 @@
         <v>7</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="6" t="n">
@@ -7936,10 +8057,10 @@
         <v>270</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="6" t="n">
@@ -7955,7 +8076,7 @@
         <v>7</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="L15" s="5"/>
       <c r="M15" s="6" t="n">
@@ -7976,13 +8097,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="6" t="n">
@@ -7998,7 +8119,7 @@
         <v>7</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="L16" s="5"/>
       <c r="M16" s="6" t="n">
@@ -8019,13 +8140,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="6" t="n">
@@ -8041,7 +8162,7 @@
         <v>7</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="L17" s="5"/>
       <c r="M17" s="6" t="n">
@@ -8062,13 +8183,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="6" t="n">
@@ -8084,7 +8205,7 @@
         <v>7</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="L18" s="5"/>
       <c r="M18" s="6" t="n">
@@ -8105,13 +8226,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="6" t="n">
@@ -8127,7 +8248,7 @@
         <v>7</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="L19" s="5"/>
       <c r="M19" s="6" t="n">
@@ -8148,13 +8269,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="6" t="n">
@@ -8170,7 +8291,7 @@
         <v>7</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="L20" s="5"/>
       <c r="M20" s="6" t="n">
@@ -8191,13 +8312,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="6" t="n">
@@ -8213,7 +8334,7 @@
         <v>7</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="L21" s="5"/>
       <c r="M21" s="6" t="n">
@@ -8237,10 +8358,10 @@
         <v>226</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="6" t="n">
@@ -8256,7 +8377,7 @@
         <v>7</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="L22" s="5" t="s">
         <v>261</v>
@@ -8279,13 +8400,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="6" t="n">
@@ -8301,7 +8422,7 @@
         <v>7</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="L23" s="5"/>
       <c r="M23" s="6" t="n">
@@ -8322,13 +8443,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="6" t="n">
@@ -8344,7 +8465,7 @@
         <v>7</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="L24" s="5"/>
       <c r="M24" s="6" t="n">
@@ -8365,13 +8486,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="6" t="n">
@@ -8387,7 +8508,7 @@
         <v>2</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="L25" s="5"/>
       <c r="M25" s="6" t="n">
@@ -8408,13 +8529,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="6" t="n">
@@ -8430,7 +8551,7 @@
         <v>7</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="L26" s="5"/>
       <c r="M26" s="6" t="n">
@@ -8451,13 +8572,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="6" t="n">
@@ -8473,7 +8594,7 @@
         <v>2</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="L27" s="5"/>
       <c r="M27" s="6" t="n">
@@ -8494,13 +8615,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="6" t="n">
@@ -8516,7 +8637,7 @@
         <v>2</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="L28" s="5"/>
       <c r="M28" s="6" t="n">
@@ -8537,13 +8658,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="6" t="n">
@@ -8559,7 +8680,7 @@
         <v>7</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="L29" s="5"/>
       <c r="M29" s="6" t="n">
@@ -8580,13 +8701,13 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="6" t="n">
@@ -8602,7 +8723,7 @@
         <v>1</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="L30" s="5"/>
       <c r="M30" s="6" t="n">
@@ -8623,13 +8744,13 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="6" t="n">
@@ -8645,7 +8766,7 @@
         <v>2</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="L31" s="5"/>
       <c r="M31" s="6" t="n">
@@ -8666,13 +8787,13 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="6" t="n">
@@ -8688,7 +8809,7 @@
         <v>2</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="L32" s="5"/>
       <c r="M32" s="6" t="n">
@@ -8709,13 +8830,13 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="6" t="n">
@@ -8731,7 +8852,7 @@
         <v>7</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="L33" s="5"/>
       <c r="M33" s="6" t="n">
@@ -8752,13 +8873,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="6" t="n">
@@ -8774,7 +8895,7 @@
         <v>7</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="L34" s="5"/>
       <c r="M34" s="6" t="n">
@@ -8795,13 +8916,13 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="6" t="n">
@@ -8817,7 +8938,7 @@
         <v>7</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="L35" s="5"/>
       <c r="M35" s="6" t="n">
@@ -8838,13 +8959,13 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="6" t="n">
@@ -8860,7 +8981,7 @@
         <v>7</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="L36" s="5"/>
       <c r="M36" s="6" t="n">
@@ -8884,10 +9005,10 @@
         <v>226</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="6" t="n">
@@ -8903,7 +9024,7 @@
         <v>7</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="L37" s="5" t="s">
         <v>261</v>
@@ -8926,13 +9047,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="6" t="n">
@@ -8948,7 +9069,7 @@
         <v>7</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="L38" s="5"/>
       <c r="M38" s="6" t="n">
@@ -8969,13 +9090,13 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="6" t="n">
@@ -8991,7 +9112,7 @@
         <v>7</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="L39" s="5"/>
       <c r="M39" s="6" t="n">
@@ -9012,13 +9133,13 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="6" t="n">
@@ -9034,7 +9155,7 @@
         <v>2</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="L40" s="5"/>
       <c r="M40" s="6" t="n">
@@ -9055,13 +9176,13 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="6" t="n">
@@ -9077,7 +9198,7 @@
         <v>2</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="L41" s="5"/>
       <c r="M41" s="6" t="n">
@@ -9098,13 +9219,13 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="6" t="n">
@@ -9120,7 +9241,7 @@
         <v>2</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="L42" s="5"/>
       <c r="M42" s="6" t="n">
@@ -9141,13 +9262,13 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="6" t="n">
@@ -9163,7 +9284,7 @@
         <v>1</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="L43" s="5"/>
       <c r="M43" s="6" t="n">
@@ -9187,10 +9308,10 @@
         <v>270</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="6" t="n">
@@ -9206,7 +9327,7 @@
         <v>2</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="L44" s="5"/>
       <c r="M44" s="6" t="n">
@@ -9227,13 +9348,13 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="6" t="n">
@@ -9268,13 +9389,13 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="6" t="n">
@@ -9309,13 +9430,13 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="6" t="n">
@@ -9350,13 +9471,13 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="6" t="n">
@@ -9394,10 +9515,10 @@
         <v>270</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="6" t="n">
@@ -9432,13 +9553,13 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="6" t="n">
@@ -9473,13 +9594,13 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="6" t="n">
@@ -9514,13 +9635,13 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="6" t="n">
@@ -9555,13 +9676,13 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="6" t="n">
@@ -9596,10 +9717,10 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="C54" s="5"/>
       <c r="D54" s="5"/>
@@ -9633,10 +9754,10 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
@@ -9670,10 +9791,10 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="C56" s="5"/>
       <c r="D56" s="5"/>
@@ -9710,7 +9831,7 @@
         <v>226</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
@@ -9748,13 +9869,13 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="6" t="n">
@@ -9781,7 +9902,7 @@
         <v>202</v>
       </c>
       <c r="P58" s="10" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="Q58" s="5" t="s">
         <v>70</v>
@@ -9789,13 +9910,13 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="6" t="n">
@@ -9822,7 +9943,7 @@
         <v>16</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="Q59" s="5" t="s">
         <v>70</v>
@@ -9830,13 +9951,13 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="6" t="n">
@@ -9863,7 +9984,7 @@
         <v>7</v>
       </c>
       <c r="P60" s="10" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="Q60" s="5" t="s">
         <v>70</v>
@@ -9871,13 +9992,13 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="6" t="n">
@@ -9904,7 +10025,7 @@
         <v>0</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="Q61" s="5" t="s">
         <v>70</v>
@@ -9915,10 +10036,10 @@
         <v>226</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="6" t="n">
@@ -9945,7 +10066,7 @@
         <v>1</v>
       </c>
       <c r="P62" s="10" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="Q62" s="5" t="s">
         <v>70</v>
@@ -9978,53 +10099,53 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="B4" s="21" t="n">
-        <f aca="false">COUNTA(Tournaments!B5:B120)</f>
-        <v>116</v>
+        <f aca="false">COUNTA(Tournaments!B5:B123)</f>
+        <v>119</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="22" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="B5" s="21" t="n">
-        <f aca="false">COUNTIF(Tournaments!P5:P120,"yes")</f>
-        <v>112</v>
+        <f aca="false">COUNTIF(Tournaments!P5:P123,"yes")</f>
+        <v>109</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="22" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="B6" s="21" t="n">
-        <f aca="false">COUNTIF(Tournaments!F5:F120,"&gt;0")</f>
-        <v>45</v>
+        <f aca="false">COUNTIF(Tournaments!F5:F123,"&gt;0")</f>
+        <v>43</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="22" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="B7" s="21" t="n">
-        <f aca="false">COUNTIFS(Tournaments!F5:F120,"&gt;0",Tournaments!I5:I120,"&lt;=7")</f>
-        <v>16</v>
+        <f aca="false">COUNTIFS(Tournaments!F5:F123,"&gt;0",Tournaments!I5:I123,"&lt;=7")</f>
+        <v>21</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="20" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="B8" s="21" t="n">
         <f aca="false">COUNTA('Perfect Drafts'!B5:B62)</f>
@@ -10033,7 +10154,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="22" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="B9" s="21" t="n">
         <f aca="false">COUNTIF('Perfect Drafts'!P5:P62,"yes")</f>
@@ -10042,7 +10163,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="22" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="B10" s="21" t="n">
         <f aca="false">COUNTIF('Perfect Drafts'!F5:F62,"&gt;0")</f>
@@ -10054,29 +10175,29 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="20" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="B12" s="21" t="n">
-        <f aca="false">SUM(Tournaments!F5:F120)+SUM('Perfect Drafts'!F5:F62)</f>
-        <v>305</v>
+        <f aca="false">SUM(Tournaments!F5:F123)+SUM('Perfect Drafts'!F5:F62)</f>
+        <v>308</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="20" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="B13" s="21" t="n">
-        <f aca="false">SUM(Tournaments!E5:E120)+SUM('Perfect Drafts'!E5:E62)</f>
-        <v>304</v>
+        <f aca="false">SUM(Tournaments!E5:E123)+SUM('Perfect Drafts'!E5:E62)</f>
+        <v>308</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="20" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="B14" s="21" t="n">
-        <f aca="false">SUM(Tournaments!J5:J120)+SUM('Perfect Drafts'!J5:J62)</f>
-        <v>383</v>
+        <f aca="false">SUM(Tournaments!J5:J123)+SUM('Perfect Drafts'!J5:J62)</f>
+        <v>369</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10084,37 +10205,37 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="23" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="23" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="23" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="23" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
   </sheetData>
